--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/52.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/52.xlsx
@@ -426,13 +426,13 @@
         <v>-13.210163891452</v>
       </c>
       <c r="E2">
-        <v>-16.26905760701906</v>
+        <v>-18.25030553741527</v>
       </c>
       <c r="F2">
-        <v>4.518557652358165</v>
+        <v>3.215708028174325</v>
       </c>
       <c r="G2">
-        <v>-16.26998221701672</v>
+        <v>-14.15533653459596</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.80509253278916</v>
       </c>
       <c r="E3">
-        <v>-16.82796356142388</v>
+        <v>-18.51860714221051</v>
       </c>
       <c r="F3">
-        <v>5.128935202906565</v>
+        <v>3.640345726197408</v>
       </c>
       <c r="G3">
-        <v>-14.90696859700518</v>
+        <v>-14.17008854690805</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.31939245140462</v>
       </c>
       <c r="E4">
-        <v>-14.64037578598754</v>
+        <v>-19.8839421395573</v>
       </c>
       <c r="F4">
-        <v>5.339564182416395</v>
+        <v>2.981815178524274</v>
       </c>
       <c r="G4">
-        <v>-14.5801621159511</v>
+        <v>-13.84566698103795</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.78434324029892</v>
       </c>
       <c r="E5">
-        <v>-17.43307814502875</v>
+        <v>-19.74735963192899</v>
       </c>
       <c r="F5">
-        <v>5.102762106447711</v>
+        <v>3.583701963193978</v>
       </c>
       <c r="G5">
-        <v>-14.84654552418846</v>
+        <v>-14.19971005503882</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.20945957401789</v>
       </c>
       <c r="E6">
-        <v>-17.79493083491576</v>
+        <v>-19.53368936890053</v>
       </c>
       <c r="F6">
-        <v>5.308591525225721</v>
+        <v>3.856047627681983</v>
       </c>
       <c r="G6">
-        <v>-13.82006863032208</v>
+        <v>-13.82153586878229</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.59835386934866</v>
       </c>
       <c r="E7">
-        <v>-19.24327191380057</v>
+        <v>-21.33782775556075</v>
       </c>
       <c r="F7">
-        <v>5.096284273357819</v>
+        <v>4.08879401684656</v>
       </c>
       <c r="G7">
-        <v>-14.52126110723099</v>
+        <v>-13.13252121001862</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.950297308962677</v>
       </c>
       <c r="E8">
-        <v>-20.49186014080642</v>
+        <v>-21.82275670984773</v>
       </c>
       <c r="F8">
-        <v>5.403598639387602</v>
+        <v>3.959277116684051</v>
       </c>
       <c r="G8">
-        <v>-13.37004022605663</v>
+        <v>-13.6095407972393</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.270857432823153</v>
       </c>
       <c r="E9">
-        <v>-18.22500832723573</v>
+        <v>-21.4801043159154</v>
       </c>
       <c r="F9">
-        <v>5.122760552286097</v>
+        <v>4.235279194888013</v>
       </c>
       <c r="G9">
-        <v>-12.96302122818518</v>
+        <v>-13.11591295830226</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.551489829291283</v>
       </c>
       <c r="E10">
-        <v>-20.84158545362494</v>
+        <v>-23.62471466056241</v>
       </c>
       <c r="F10">
-        <v>5.965177066237082</v>
+        <v>4.328889681608774</v>
       </c>
       <c r="G10">
-        <v>-13.90465806044645</v>
+        <v>-12.77454243854665</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.802680925228915</v>
       </c>
       <c r="E11">
-        <v>-20.94165708049668</v>
+        <v>-23.87492487682671</v>
       </c>
       <c r="F11">
-        <v>6.025676051133141</v>
+        <v>4.669580627032155</v>
       </c>
       <c r="G11">
-        <v>-12.34897932184452</v>
+        <v>-12.66270727786942</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.032474092129712</v>
       </c>
       <c r="E12">
-        <v>-22.15359737077225</v>
+        <v>-25.29823455105678</v>
       </c>
       <c r="F12">
-        <v>6.456473489163441</v>
+        <v>5.17870682993637</v>
       </c>
       <c r="G12">
-        <v>-11.11084283711511</v>
+        <v>-11.46367060950882</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.243466196649379</v>
       </c>
       <c r="E13">
-        <v>-23.17845210370959</v>
+        <v>-25.96604185960993</v>
       </c>
       <c r="F13">
-        <v>6.450613618156037</v>
+        <v>5.062124058401173</v>
       </c>
       <c r="G13">
-        <v>-11.38675676848233</v>
+        <v>-11.36113231032055</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.459004684775844</v>
       </c>
       <c r="E14">
-        <v>-23.72457447365659</v>
+        <v>-26.44016000481838</v>
       </c>
       <c r="F14">
-        <v>6.304239441346559</v>
+        <v>5.811398941581382</v>
       </c>
       <c r="G14">
-        <v>-10.60675374460148</v>
+        <v>-11.08474844492694</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.680914636253931</v>
       </c>
       <c r="E15">
-        <v>-25.86877365038245</v>
+        <v>-27.80044054398285</v>
       </c>
       <c r="F15">
-        <v>6.683666503259651</v>
+        <v>5.862139758472463</v>
       </c>
       <c r="G15">
-        <v>-9.93170265328339</v>
+        <v>-10.8874871104839</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.911135857677384</v>
       </c>
       <c r="E16">
-        <v>-24.27124091428715</v>
+        <v>-28.31464548489855</v>
       </c>
       <c r="F16">
-        <v>6.923868199049423</v>
+        <v>6.014947036532082</v>
       </c>
       <c r="G16">
-        <v>-10.90379773731688</v>
+        <v>-9.954973525196278</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.154392361272512</v>
       </c>
       <c r="E17">
-        <v>-25.24288470373079</v>
+        <v>-28.88304152718061</v>
       </c>
       <c r="F17">
-        <v>7.900960685347552</v>
+        <v>6.164621429074313</v>
       </c>
       <c r="G17">
-        <v>-9.830803901698339</v>
+        <v>-9.93662651758223</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.399005403954193</v>
       </c>
       <c r="E18">
-        <v>-28.20467052562275</v>
+        <v>-30.23474568495931</v>
       </c>
       <c r="F18">
-        <v>7.569426513194717</v>
+        <v>6.787702822112045</v>
       </c>
       <c r="G18">
-        <v>-9.423399818999702</v>
+        <v>-9.297372650725187</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.650678238697727</v>
       </c>
       <c r="E19">
-        <v>-29.00607002965034</v>
+        <v>-30.00225722141806</v>
       </c>
       <c r="F19">
-        <v>7.925652660890199</v>
+        <v>6.876972663642137</v>
       </c>
       <c r="G19">
-        <v>-7.938063677288438</v>
+        <v>-8.643561272028094</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.9153732606913567</v>
       </c>
       <c r="E20">
-        <v>-28.87531863072209</v>
+        <v>-31.22635396124139</v>
       </c>
       <c r="F20">
-        <v>8.354124043253439</v>
+        <v>6.741764879422396</v>
       </c>
       <c r="G20">
-        <v>-7.91408790433595</v>
+        <v>-8.285598165023666</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.1969790853240208</v>
       </c>
       <c r="E21">
-        <v>-30.49730132188666</v>
+        <v>-32.66369318332673</v>
       </c>
       <c r="F21">
-        <v>8.117063516655081</v>
+        <v>6.861480536474981</v>
       </c>
       <c r="G21">
-        <v>-8.099273239672797</v>
+        <v>-7.847763243371012</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.4805788009511242</v>
       </c>
       <c r="E22">
-        <v>-29.36108238048536</v>
+        <v>-33.23085572184532</v>
       </c>
       <c r="F22">
-        <v>8.804040200940351</v>
+        <v>7.456321228016472</v>
       </c>
       <c r="G22">
-        <v>-7.704858916687244</v>
+        <v>-6.74636842271805</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.102542258690062</v>
       </c>
       <c r="E23">
-        <v>-28.81675835104201</v>
+        <v>-33.6321140807823</v>
       </c>
       <c r="F23">
-        <v>8.467467898243688</v>
+        <v>7.409826622432141</v>
       </c>
       <c r="G23">
-        <v>-6.751130420852241</v>
+        <v>-7.100769168727905</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.647859071842731</v>
       </c>
       <c r="E24">
-        <v>-30.7043036041331</v>
+        <v>-32.76191455455326</v>
       </c>
       <c r="F24">
-        <v>8.335366491784447</v>
+        <v>7.305594808872685</v>
       </c>
       <c r="G24">
-        <v>-6.044427967483785</v>
+        <v>-6.115549871634894</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.093064239541157</v>
       </c>
       <c r="E25">
-        <v>-32.18050027137353</v>
+        <v>-33.99560521253696</v>
       </c>
       <c r="F25">
-        <v>9.32208626403791</v>
+        <v>7.101627560016168</v>
       </c>
       <c r="G25">
-        <v>-6.213309202849131</v>
+        <v>-5.787303564938812</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.422985628832432</v>
       </c>
       <c r="E26">
-        <v>-31.38188341893357</v>
+        <v>-34.28841699396568</v>
       </c>
       <c r="F26">
-        <v>8.151657796130793</v>
+        <v>7.530284496677634</v>
       </c>
       <c r="G26">
-        <v>-6.213659042624339</v>
+        <v>-5.390741904527068</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.621048593283718</v>
       </c>
       <c r="E27">
-        <v>-29.93798212295501</v>
+        <v>-34.93577596656105</v>
       </c>
       <c r="F27">
-        <v>9.013535973843151</v>
+        <v>7.330401099116919</v>
       </c>
       <c r="G27">
-        <v>-6.633931485412575</v>
+        <v>-5.991375026647773</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.679694031092739</v>
       </c>
       <c r="E28">
-        <v>-30.26759135672171</v>
+        <v>-34.46057798640814</v>
       </c>
       <c r="F28">
-        <v>8.757012126748617</v>
+        <v>7.202910385621658</v>
       </c>
       <c r="G28">
-        <v>-5.423028982885366</v>
+        <v>-5.347834317172121</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.59395284371136</v>
       </c>
       <c r="E29">
-        <v>-30.14019782914959</v>
+        <v>-34.11315978248057</v>
       </c>
       <c r="F29">
-        <v>7.804205715965764</v>
+        <v>6.604244293414039</v>
       </c>
       <c r="G29">
-        <v>-5.164669698148795</v>
+        <v>-5.847538664144977</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.362774518520682</v>
       </c>
       <c r="E30">
-        <v>-29.61672499716253</v>
+        <v>-33.63718515180992</v>
       </c>
       <c r="F30">
-        <v>8.044327888484867</v>
+        <v>7.141851424361307</v>
       </c>
       <c r="G30">
-        <v>-5.880974470123365</v>
+        <v>-5.618686014777169</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.991709513079357</v>
       </c>
       <c r="E31">
-        <v>-30.61419345462395</v>
+        <v>-33.7083753471288</v>
       </c>
       <c r="F31">
-        <v>8.190183507300194</v>
+        <v>6.986338698364144</v>
       </c>
       <c r="G31">
-        <v>-5.687792424103938</v>
+        <v>-5.298833251941516</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.492768993268366</v>
       </c>
       <c r="E32">
-        <v>-30.64770987001532</v>
+        <v>-33.61065028465559</v>
       </c>
       <c r="F32">
-        <v>7.682805159615885</v>
+        <v>6.643732567505491</v>
       </c>
       <c r="G32">
-        <v>-5.823149088174797</v>
+        <v>-5.513715807002277</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.8895671137795953</v>
       </c>
       <c r="E33">
-        <v>-30.04073880094825</v>
+        <v>-33.78585142778782</v>
       </c>
       <c r="F33">
-        <v>7.569022269902151</v>
+        <v>6.868462016945775</v>
       </c>
       <c r="G33">
-        <v>-6.301523651838258</v>
+        <v>-5.638652989410003</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.2030651281002055</v>
       </c>
       <c r="E34">
-        <v>-31.36180056557237</v>
+        <v>-32.71027767815167</v>
       </c>
       <c r="F34">
-        <v>7.956898679323797</v>
+        <v>6.610856322023185</v>
       </c>
       <c r="G34">
-        <v>-6.973307396300573</v>
+        <v>-5.476927804968899</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.5359029631472531</v>
       </c>
       <c r="E35">
-        <v>-29.44988842163851</v>
+        <v>-32.03543482961425</v>
       </c>
       <c r="F35">
-        <v>8.753957107767093</v>
+        <v>7.301870469029699</v>
       </c>
       <c r="G35">
-        <v>-6.919045680718874</v>
+        <v>-5.662570020609192</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.294053966665941</v>
       </c>
       <c r="E36">
-        <v>-28.83753686730013</v>
+        <v>-32.34256273047966</v>
       </c>
       <c r="F36">
-        <v>7.726635735632812</v>
+        <v>6.709362460094491</v>
       </c>
       <c r="G36">
-        <v>-7.528819019653066</v>
+        <v>-6.062486487820516</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.044022534439949</v>
       </c>
       <c r="E37">
-        <v>-28.32510950083146</v>
+        <v>-31.43432601833218</v>
       </c>
       <c r="F37">
-        <v>7.791395842448872</v>
+        <v>6.895524779995235</v>
       </c>
       <c r="G37">
-        <v>-6.030055818509707</v>
+        <v>-5.996938523371435</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.750827325628497</v>
       </c>
       <c r="E38">
-        <v>-29.18023286995136</v>
+        <v>-31.19561604422634</v>
       </c>
       <c r="F38">
-        <v>7.81564381306362</v>
+        <v>6.685621450330257</v>
       </c>
       <c r="G38">
-        <v>-6.621144058405301</v>
+        <v>-6.342162502143527</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.392184387321391</v>
       </c>
       <c r="E39">
-        <v>-27.37687113380889</v>
+        <v>-31.34543483634688</v>
       </c>
       <c r="F39">
-        <v>8.895192093209602</v>
+        <v>6.571199060981561</v>
       </c>
       <c r="G39">
-        <v>-7.405871224623769</v>
+        <v>-6.584739835826817</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.950506253204624</v>
       </c>
       <c r="E40">
-        <v>-26.1855349249158</v>
+        <v>-30.26167718379516</v>
       </c>
       <c r="F40">
-        <v>8.773256411517515</v>
+        <v>7.046975192249069</v>
       </c>
       <c r="G40">
-        <v>-6.309611738581526</v>
+        <v>-5.902980436281859</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.410475049879429</v>
       </c>
       <c r="E41">
-        <v>-28.49407252055379</v>
+        <v>-29.85391697252915</v>
       </c>
       <c r="F41">
-        <v>8.224532590024678</v>
+        <v>7.048312177237187</v>
       </c>
       <c r="G41">
-        <v>-6.925259252845724</v>
+        <v>-5.896853018726516</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.77441300559649</v>
       </c>
       <c r="E42">
-        <v>-26.80174688918061</v>
+        <v>-28.76816370193585</v>
       </c>
       <c r="F42">
-        <v>8.374516791975557</v>
+        <v>6.738103495502022</v>
       </c>
       <c r="G42">
-        <v>-6.748122843083278</v>
+        <v>-6.528358195637136</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.04387020249846</v>
       </c>
       <c r="E43">
-        <v>-25.16707198420737</v>
+        <v>-29.2108835695286</v>
       </c>
       <c r="F43">
-        <v>8.07803415810478</v>
+        <v>6.827843849716905</v>
       </c>
       <c r="G43">
-        <v>-7.86023477028276</v>
+        <v>-6.48899599943692</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.227169497186259</v>
       </c>
       <c r="E44">
-        <v>-26.03093163334905</v>
+        <v>-27.83343780795861</v>
       </c>
       <c r="F44">
-        <v>8.660719386377592</v>
+        <v>6.68712245206413</v>
       </c>
       <c r="G44">
-        <v>-7.774513582378146</v>
+        <v>-5.962672500613073</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.34125118928537</v>
       </c>
       <c r="E45">
-        <v>-24.41696048683009</v>
+        <v>-27.315449291526</v>
       </c>
       <c r="F45">
-        <v>8.500455144957971</v>
+        <v>6.741851029632287</v>
       </c>
       <c r="G45">
-        <v>-7.939855953450238</v>
+        <v>-6.327657205195301</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.398455187882642</v>
       </c>
       <c r="E46">
-        <v>-25.73465399706976</v>
+        <v>-27.06909325537114</v>
       </c>
       <c r="F46">
-        <v>8.343348640077823</v>
+        <v>7.526464066215923</v>
       </c>
       <c r="G46">
-        <v>-7.71905875651831</v>
+        <v>-6.214311728772119</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.418042127267882</v>
       </c>
       <c r="E47">
-        <v>-24.818090096216</v>
+        <v>-26.79079487091703</v>
       </c>
       <c r="F47">
-        <v>8.249178176992769</v>
+        <v>7.58502135791982</v>
       </c>
       <c r="G47">
-        <v>-8.101842212350453</v>
+        <v>-6.55493818631926</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.419268097414993</v>
       </c>
       <c r="E48">
-        <v>-22.23861775980281</v>
+        <v>-25.4544742078855</v>
       </c>
       <c r="F48">
-        <v>8.267432081080859</v>
+        <v>7.337975690648118</v>
       </c>
       <c r="G48">
-        <v>-6.949186727023277</v>
+        <v>-6.781892824369328</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.414810302597621</v>
       </c>
       <c r="E49">
-        <v>-23.16102522899061</v>
+        <v>-25.55199991621513</v>
       </c>
       <c r="F49">
-        <v>7.965122710898791</v>
+        <v>7.458822897572927</v>
       </c>
       <c r="G49">
-        <v>-6.756080392596991</v>
+        <v>-7.073074390105376</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.421199437387214</v>
       </c>
       <c r="E50">
-        <v>-21.36969949926748</v>
+        <v>-24.81002040661186</v>
       </c>
       <c r="F50">
-        <v>8.776955900338418</v>
+        <v>7.436794951597682</v>
       </c>
       <c r="G50">
-        <v>-7.948569313523079</v>
+        <v>-6.671612362096113</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.45033008233753</v>
       </c>
       <c r="E51">
-        <v>-20.89850936804304</v>
+        <v>-24.2311375057346</v>
       </c>
       <c r="F51">
-        <v>8.071264739689102</v>
+        <v>7.401768264337708</v>
       </c>
       <c r="G51">
-        <v>-8.550754523303199</v>
+        <v>-6.561188308870385</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.507880812002669</v>
       </c>
       <c r="E52">
-        <v>-20.31603809258113</v>
+        <v>-24.04072522612519</v>
       </c>
       <c r="F52">
-        <v>8.574676864248806</v>
+        <v>7.521770536511661</v>
       </c>
       <c r="G52">
-        <v>-8.174661100485784</v>
+        <v>-7.101126840736888</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.600341058573738</v>
       </c>
       <c r="E53">
-        <v>-21.56920731167827</v>
+        <v>-23.72687119951922</v>
       </c>
       <c r="F53">
-        <v>8.371188411751108</v>
+        <v>7.545536397297979</v>
       </c>
       <c r="G53">
-        <v>-7.560779754937475</v>
+        <v>-6.785440826268652</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.72628191276259</v>
       </c>
       <c r="E54">
-        <v>-18.55295419986684</v>
+        <v>-22.32549463429558</v>
       </c>
       <c r="F54">
-        <v>8.501669531570474</v>
+        <v>7.501154128590787</v>
       </c>
       <c r="G54">
-        <v>-8.726794420337377</v>
+        <v>-7.639754778818652</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.887275412111013</v>
       </c>
       <c r="E55">
-        <v>-19.43501322103393</v>
+        <v>-21.87481721380446</v>
       </c>
       <c r="F55">
-        <v>8.00542112831018</v>
+        <v>7.420288902729499</v>
       </c>
       <c r="G55">
-        <v>-8.035111580601598</v>
+        <v>-7.825094148086375</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.088398259398594</v>
       </c>
       <c r="E56">
-        <v>-17.63311756848912</v>
+        <v>-21.37896116052185</v>
       </c>
       <c r="F56">
-        <v>8.555288096818881</v>
+        <v>7.617090773551801</v>
       </c>
       <c r="G56">
-        <v>-9.206341208322248</v>
+        <v>-7.418825739284872</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.327353257645534</v>
       </c>
       <c r="E57">
-        <v>-17.87264987843728</v>
+        <v>-21.11487921843263</v>
       </c>
       <c r="F57">
-        <v>8.294927251914579</v>
+        <v>7.377412605960597</v>
       </c>
       <c r="G57">
-        <v>-7.900115199284311</v>
+        <v>-8.277627561786996</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.610904922651109</v>
       </c>
       <c r="E58">
-        <v>-18.58995931277107</v>
+        <v>-20.25876530841175</v>
       </c>
       <c r="F58">
-        <v>7.729921040752315</v>
+        <v>7.676163309780239</v>
       </c>
       <c r="G58">
-        <v>-9.203333630553285</v>
+        <v>-8.387357156951488</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.942180755874948</v>
       </c>
       <c r="E59">
-        <v>-17.93070761954706</v>
+        <v>-20.26454657857591</v>
       </c>
       <c r="F59">
-        <v>8.404077911111859</v>
+        <v>7.170438383431918</v>
       </c>
       <c r="G59">
-        <v>-9.810232539692663</v>
+        <v>-8.353112020149855</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.31886834818562</v>
       </c>
       <c r="E60">
-        <v>-16.65884064306554</v>
+        <v>-19.79644643657713</v>
       </c>
       <c r="F60">
-        <v>8.780164995656863</v>
+        <v>7.274468075345091</v>
       </c>
       <c r="G60">
-        <v>-9.316120407633971</v>
+        <v>-8.88544414765015</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.744602117806416</v>
       </c>
       <c r="E61">
-        <v>-17.31938813822289</v>
+        <v>-19.14334564932519</v>
       </c>
       <c r="F61">
-        <v>7.640034893874541</v>
+        <v>6.83176037079734</v>
       </c>
       <c r="G61">
-        <v>-9.537558542363017</v>
+        <v>-8.514375102798331</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.210399828330699</v>
       </c>
       <c r="E62">
-        <v>-16.39705958005027</v>
+        <v>-18.81672049789538</v>
       </c>
       <c r="F62">
-        <v>7.745547363438726</v>
+        <v>7.100280634619216</v>
       </c>
       <c r="G62">
-        <v>-8.246337787862505</v>
+        <v>-8.66065512223841</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.712691268149449</v>
       </c>
       <c r="E63">
-        <v>-14.69558027091716</v>
+        <v>-19.36489870744817</v>
       </c>
       <c r="F63">
-        <v>7.682561619599462</v>
+        <v>7.030880013612674</v>
       </c>
       <c r="G63">
-        <v>-9.673960809642617</v>
+        <v>-9.363773023283265</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.245611668959995</v>
       </c>
       <c r="E64">
-        <v>-15.59996695616653</v>
+        <v>-18.70715462993508</v>
       </c>
       <c r="F64">
-        <v>8.721327715770819</v>
+        <v>6.599078594290181</v>
       </c>
       <c r="G64">
-        <v>-10.73868772251339</v>
+        <v>-9.06614291840717</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.790557792905501</v>
       </c>
       <c r="E65">
-        <v>-14.92845498311163</v>
+        <v>-18.43114881813227</v>
       </c>
       <c r="F65">
-        <v>7.741322689684448</v>
+        <v>6.671979895940955</v>
       </c>
       <c r="G65">
-        <v>-9.540358565936986</v>
+        <v>-9.496821789135581</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.33800706311044</v>
       </c>
       <c r="E66">
-        <v>-15.69474323859912</v>
+        <v>-17.69425699240192</v>
       </c>
       <c r="F66">
-        <v>8.156119382962272</v>
+        <v>6.463463253308263</v>
       </c>
       <c r="G66">
-        <v>-9.652739372233754</v>
+        <v>-9.533030205869732</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.87217696598424</v>
       </c>
       <c r="E67">
-        <v>-14.81432473590534</v>
+        <v>-17.96757152326624</v>
       </c>
       <c r="F67">
-        <v>8.458589456420484</v>
+        <v>6.582453260515996</v>
       </c>
       <c r="G67">
-        <v>-9.829931913004907</v>
+        <v>-9.940810235789488</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.37286483585288</v>
       </c>
       <c r="E68">
-        <v>-14.64340347704334</v>
+        <v>-16.876576899981</v>
       </c>
       <c r="F68">
-        <v>7.670435977557283</v>
+        <v>6.798483195492079</v>
       </c>
       <c r="G68">
-        <v>-10.00415473180367</v>
+        <v>-9.861467096920965</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.8280447917492</v>
       </c>
       <c r="E69">
-        <v>-16.44251647800052</v>
+        <v>-17.51950647269843</v>
       </c>
       <c r="F69">
-        <v>7.500768109381083</v>
+        <v>6.333492407809021</v>
       </c>
       <c r="G69">
-        <v>-9.397147476763763</v>
+        <v>-9.65944768046062</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.21803882981193</v>
       </c>
       <c r="E70">
-        <v>-14.92188875600707</v>
+        <v>-16.09998868040794</v>
       </c>
       <c r="F70">
-        <v>7.867146727965276</v>
+        <v>6.370169202935371</v>
       </c>
       <c r="G70">
-        <v>-9.414117316605999</v>
+        <v>-9.281229111546038</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.53386226607871</v>
       </c>
       <c r="E71">
-        <v>-14.47403136600551</v>
+        <v>-16.7687013890299</v>
       </c>
       <c r="F71">
-        <v>7.980964409109927</v>
+        <v>6.051575786349071</v>
       </c>
       <c r="G71">
-        <v>-10.88202934891617</v>
+        <v>-9.616598834858973</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.77106673010913</v>
       </c>
       <c r="E72">
-        <v>-13.20241773541481</v>
+        <v>-17.20090117233686</v>
       </c>
       <c r="F72">
-        <v>7.158142097704762</v>
+        <v>6.5483079561726</v>
       </c>
       <c r="G72">
-        <v>-9.917386635318021</v>
+        <v>-9.453992524118368</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.92042868306346</v>
       </c>
       <c r="E73">
-        <v>-11.69667096959822</v>
+        <v>-16.15426699921212</v>
       </c>
       <c r="F73">
-        <v>7.042029838854355</v>
+        <v>6.325336302361057</v>
       </c>
       <c r="G73">
-        <v>-9.606359494572626</v>
+        <v>-9.603794438011857</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.98197850187282</v>
       </c>
       <c r="E74">
-        <v>-14.27908377962938</v>
+        <v>-16.66951439617035</v>
       </c>
       <c r="F74">
-        <v>6.772596714154594</v>
+        <v>5.820570625465178</v>
       </c>
       <c r="G74">
-        <v>-9.588026846053829</v>
+        <v>-9.681592016082442</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.96039845799662</v>
       </c>
       <c r="E75">
-        <v>-13.66545511280862</v>
+        <v>-16.48823087505291</v>
       </c>
       <c r="F75">
-        <v>7.221180857057805</v>
+        <v>6.012485128610962</v>
       </c>
       <c r="G75">
-        <v>-9.910588256402761</v>
+        <v>-9.326299700794721</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.85632634468551</v>
       </c>
       <c r="E76">
-        <v>-13.25820782314123</v>
+        <v>-16.78455419665677</v>
       </c>
       <c r="F76">
-        <v>7.355209046095958</v>
+        <v>5.430149471382132</v>
       </c>
       <c r="G76">
-        <v>-9.132343569004028</v>
+        <v>-9.16635112804787</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.67797196322135</v>
       </c>
       <c r="E77">
-        <v>-15.39371017535289</v>
+        <v>-17.56165326122279</v>
       </c>
       <c r="F77">
-        <v>6.89085113110864</v>
+        <v>5.515202922831974</v>
       </c>
       <c r="G77">
-        <v>-8.074512937970679</v>
+        <v>-9.151586062012829</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.43234258938944</v>
       </c>
       <c r="E78">
-        <v>-15.83722745952001</v>
+        <v>-15.95858014122017</v>
       </c>
       <c r="F78">
-        <v>7.206487276066947</v>
+        <v>5.536564861415368</v>
       </c>
       <c r="G78">
-        <v>-8.65413870373899</v>
+        <v>-8.999273917194985</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.12528940943111</v>
       </c>
       <c r="E79">
-        <v>-15.57325350092523</v>
+        <v>-17.42210120749723</v>
       </c>
       <c r="F79">
-        <v>7.310813523510323</v>
+        <v>5.70839642524768</v>
       </c>
       <c r="G79">
-        <v>-7.977193517220044</v>
+        <v>-8.421492642480294</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.76824659103004</v>
       </c>
       <c r="E80">
-        <v>-16.57415251094096</v>
+        <v>-17.22078259494882</v>
       </c>
       <c r="F80">
-        <v>7.025286876908972</v>
+        <v>5.413870395182316</v>
       </c>
       <c r="G80">
-        <v>-9.508918674198505</v>
+        <v>-8.607754909960976</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.36577987904674</v>
       </c>
       <c r="E81">
-        <v>-19.02295235944107</v>
+        <v>-18.60848678849113</v>
       </c>
       <c r="F81">
-        <v>7.40561851602592</v>
+        <v>5.606454219189562</v>
       </c>
       <c r="G81">
-        <v>-8.633720070291893</v>
+        <v>-8.391390757344759</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.91796415880123</v>
       </c>
       <c r="E82">
-        <v>-18.55849043056284</v>
+        <v>-18.746751346706</v>
       </c>
       <c r="F82">
-        <v>7.681231261550566</v>
+        <v>5.563644191812883</v>
       </c>
       <c r="G82">
-        <v>-7.344552666412291</v>
+        <v>-7.446831196513744</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.43571953111037</v>
       </c>
       <c r="E83">
-        <v>-18.11833309435751</v>
+        <v>-21.15953454659719</v>
       </c>
       <c r="F83">
-        <v>7.226899905606732</v>
+        <v>5.33418642123742</v>
       </c>
       <c r="G83">
-        <v>-6.580439939485254</v>
+        <v>-7.618140424348825</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.916452325725674</v>
       </c>
       <c r="E84">
-        <v>-21.29602153036503</v>
+        <v>-21.37354537295428</v>
       </c>
       <c r="F84">
-        <v>6.661898664648885</v>
+        <v>5.248534888522757</v>
       </c>
       <c r="G84">
-        <v>-7.68205406268387</v>
+        <v>-7.529427323142796</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.360703353692305</v>
       </c>
       <c r="E85">
-        <v>-21.10821331425628</v>
+        <v>-21.65006618296136</v>
       </c>
       <c r="F85">
-        <v>6.793526244953726</v>
+        <v>5.419983746614976</v>
       </c>
       <c r="G85">
-        <v>-7.615271216043192</v>
+        <v>-8.24111238256339</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.775306567919504</v>
       </c>
       <c r="E86">
-        <v>-20.23582296905339</v>
+        <v>-22.74398466701928</v>
       </c>
       <c r="F86">
-        <v>6.767923065267999</v>
+        <v>5.463350436886336</v>
       </c>
       <c r="G86">
-        <v>-6.230310371626461</v>
+        <v>-6.912171590210473</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.158161501586651</v>
       </c>
       <c r="E87">
-        <v>-23.75137099312439</v>
+        <v>-23.81770193119322</v>
       </c>
       <c r="F87">
-        <v>6.551308302905539</v>
+        <v>5.089629169643728</v>
       </c>
       <c r="G87">
-        <v>-5.351941018413942</v>
+        <v>-6.834635086599</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.519507921071792</v>
       </c>
       <c r="E88">
-        <v>-23.74092151343112</v>
+        <v>-24.43746904435209</v>
       </c>
       <c r="F88">
-        <v>6.456932404704592</v>
+        <v>4.964413153036555</v>
       </c>
       <c r="G88">
-        <v>-6.521781730012121</v>
+        <v>-6.947476689316098</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.867108343137917</v>
       </c>
       <c r="E89">
-        <v>-23.4439378312266</v>
+        <v>-26.03078627095269</v>
       </c>
       <c r="F89">
-        <v>5.993394573446045</v>
+        <v>4.738217493293316</v>
       </c>
       <c r="G89">
-        <v>-5.863803602947613</v>
+        <v>-6.507550561245963</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.202172433795227</v>
       </c>
       <c r="E90">
-        <v>-27.03773650986869</v>
+        <v>-28.03364335987197</v>
       </c>
       <c r="F90">
-        <v>6.365606555280752</v>
+        <v>4.771648744935498</v>
       </c>
       <c r="G90">
-        <v>-5.536656419724389</v>
+        <v>-6.086996158041888</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.543600528581582</v>
       </c>
       <c r="E91">
-        <v>-27.23298728067153</v>
+        <v>-28.85281653176417</v>
       </c>
       <c r="F91">
-        <v>6.227915325587418</v>
+        <v>4.611725790885831</v>
       </c>
       <c r="G91">
-        <v>-5.873828862177488</v>
+        <v>-6.110111690651605</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.896662267601587</v>
       </c>
       <c r="E92">
-        <v>-28.33136008387532</v>
+        <v>-30.94594574543427</v>
       </c>
       <c r="F92">
-        <v>5.822861889701321</v>
+        <v>4.376502583186884</v>
       </c>
       <c r="G92">
-        <v>-5.666039700170781</v>
+        <v>-6.535341937418363</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.26815905051097</v>
       </c>
       <c r="E93">
-        <v>-31.44456160764222</v>
+        <v>-32.20319964786938</v>
       </c>
       <c r="F93">
-        <v>5.277927020708889</v>
+        <v>4.178728209033697</v>
       </c>
       <c r="G93">
-        <v>-4.795784541147444</v>
+        <v>-6.017487694048087</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.669858579633009</v>
       </c>
       <c r="E94">
-        <v>-32.79111163016681</v>
+        <v>-33.89383699883902</v>
       </c>
       <c r="F94">
-        <v>5.363404596268964</v>
+        <v>3.993566556955534</v>
       </c>
       <c r="G94">
-        <v>-5.64870435608579</v>
+        <v>-5.740143074644941</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.09932275910571</v>
       </c>
       <c r="E95">
-        <v>-36.09540240698907</v>
+        <v>-36.06659780984572</v>
       </c>
       <c r="F95">
-        <v>4.98320715267127</v>
+        <v>3.662451538708515</v>
       </c>
       <c r="G95">
-        <v>-6.503898129562995</v>
+        <v>-5.838077325746783</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.560704504830872</v>
       </c>
       <c r="E96">
-        <v>-38.16190745946136</v>
+        <v>-38.19136411078271</v>
       </c>
       <c r="F96">
-        <v>4.965993678041096</v>
+        <v>3.097244862634774</v>
       </c>
       <c r="G96">
-        <v>-4.589788960674832</v>
+        <v>-5.527766834391649</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.056795101948429</v>
       </c>
       <c r="E97">
-        <v>-39.84227807203602</v>
+        <v>-40.41429986780466</v>
       </c>
       <c r="F97">
-        <v>4.777989069036526</v>
+        <v>3.026954575037625</v>
       </c>
       <c r="G97">
-        <v>-5.584072762988189</v>
+        <v>-6.015696723258584</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.577386380950614</v>
       </c>
       <c r="E98">
-        <v>-40.84768954615618</v>
+        <v>-41.93109417574529</v>
       </c>
       <c r="F98">
-        <v>4.035698979796723</v>
+        <v>2.623418708233456</v>
       </c>
       <c r="G98">
-        <v>-5.156845296609228</v>
+        <v>-6.076665441694852</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.134840751141893</v>
       </c>
       <c r="E99">
-        <v>-44.6426344790767</v>
+        <v>-44.63180913375854</v>
       </c>
       <c r="F99">
-        <v>2.780086178390122</v>
+        <v>2.707469835125911</v>
       </c>
       <c r="G99">
-        <v>-6.702818592193689</v>
+        <v>-5.993205158606143</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7180838734407832</v>
       </c>
       <c r="E100">
-        <v>-45.82571410385604</v>
+        <v>-46.19698420042209</v>
       </c>
       <c r="F100">
-        <v>3.382383833291614</v>
+        <v>2.249167285853057</v>
       </c>
       <c r="G100">
-        <v>-5.261121046322884</v>
+        <v>-6.228156507338792</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.3421119844337292</v>
       </c>
       <c r="E101">
-        <v>-49.28996477655124</v>
+        <v>-48.92738838959087</v>
       </c>
       <c r="F101">
-        <v>2.105858068433937</v>
+        <v>1.722564187484577</v>
       </c>
       <c r="G101">
-        <v>-6.474025989951476</v>
+        <v>-6.204988759837253</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.008266039708782693</v>
       </c>
       <c r="E102">
-        <v>-52.00616394468627</v>
+        <v>-50.79640512865907</v>
       </c>
       <c r="F102">
-        <v>2.387507955590185</v>
+        <v>1.725564534217517</v>
       </c>
       <c r="G102">
-        <v>-6.125193962154466</v>
+        <v>-6.474723058757304</v>
       </c>
     </row>
   </sheetData>
